--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,39 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R5" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R6" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>130604048</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130604188</v>
+        <v>130609986</v>
       </c>
       <c r="B3" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,30 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745626</v>
+        <v>745431</v>
       </c>
       <c r="R3" t="n">
-        <v>7101693</v>
+        <v>7101733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130609986</v>
+        <v>130604188</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,34 +910,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745431</v>
+        <v>745626</v>
       </c>
       <c r="R4" t="n">
-        <v>7101733</v>
+        <v>7101693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130609986</v>
+        <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745431</v>
+        <v>745626</v>
       </c>
       <c r="R3" t="n">
-        <v>7101733</v>
+        <v>7101693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130604188</v>
+        <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +901,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745626</v>
+        <v>745431</v>
       </c>
       <c r="R4" t="n">
-        <v>7101693</v>
+        <v>7101733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +970,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,34 +1013,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R5" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,12 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1194,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,39 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R5" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R6" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130610008</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,34 +1013,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R5" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,12 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1194,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>130604048</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,39 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R5" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R6" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,34 +1013,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R5" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,12 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1194,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130610008</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,39 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R5" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>57862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R6" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>130604048</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130610008</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>130604048</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130610008</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B5" t="n">
-        <v>58022</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,34 +1013,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R5" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,12 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1194,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>130604048</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,39 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R5" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R6" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609984</v>
+        <v>130604224</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,34 +1013,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745512</v>
+        <v>745576</v>
       </c>
       <c r="R5" t="n">
-        <v>7101717</v>
+        <v>7101686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,12 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130609984</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745512</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1194,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130604188</v>
+        <v>130609986</v>
       </c>
       <c r="B3" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,30 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745626</v>
+        <v>745431</v>
       </c>
       <c r="R3" t="n">
-        <v>7101693</v>
+        <v>7101733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130609986</v>
+        <v>130604188</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,34 +910,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745431</v>
+        <v>745626</v>
       </c>
       <c r="R4" t="n">
-        <v>7101733</v>
+        <v>7101693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130609986</v>
+        <v>130604188</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745431</v>
+        <v>745626</v>
       </c>
       <c r="R3" t="n">
-        <v>7101733</v>
+        <v>7101693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130604188</v>
+        <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>91804</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +901,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745626</v>
+        <v>745431</v>
       </c>
       <c r="R4" t="n">
-        <v>7101693</v>
+        <v>7101733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +970,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130611551</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130611551</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130611551</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130611551</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130611551</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130610008</v>
+        <v>130604048</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,16 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745522</v>
+        <v>745605</v>
       </c>
       <c r="R2" t="n">
-        <v>7101705</v>
+        <v>7101733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130611551</v>
+        <v>130604224</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,40 +815,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västansjö, Vb</t>
+          <t>Västansjö, Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745582</v>
+        <v>745576</v>
       </c>
       <c r="R3" t="n">
-        <v>7101809</v>
+        <v>7101686</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,27 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En individ födosökte på gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130604188</v>
+        <v>130609986</v>
       </c>
       <c r="B4" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,30 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745626</v>
+        <v>745431</v>
       </c>
       <c r="R4" t="n">
-        <v>7101693</v>
+        <v>7101733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609986</v>
+        <v>130610008</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745431</v>
+        <v>745522</v>
       </c>
       <c r="R5" t="n">
-        <v>7101733</v>
+        <v>7101705</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130604224</v>
+        <v>130611551</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,25 +1151,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västansjö, Västansjö, Vb</t>
+          <t>Västansjö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745576</v>
+        <v>745582</v>
       </c>
       <c r="R6" t="n">
-        <v>7101686</v>
+        <v>7101809</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,22 +1208,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En individ födosökte på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1258,7 @@
         <v>130609984</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,118 +1364,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130604048</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Västansjö, Västansjö, Vb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>745605</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7101733</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 258-2026 artfynd.xlsx
+++ b/artfynd/A 258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130604048</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130604224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130610008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130611551</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,8 +1394,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609984</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>